--- a/Salidas/tabla_resumen.xlsx
+++ b/Salidas/tabla_resumen.xlsx
@@ -508,22 +508,22 @@
         <v>10</v>
       </c>
       <c r="C6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D6">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E6">
         <v>155845</v>
       </c>
       <c r="F6">
-        <v>10.9</v>
+        <v>11.5</v>
       </c>
       <c r="G6">
         <v>6.4</v>
       </c>
       <c r="H6">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="7">
@@ -531,22 +531,22 @@
         <v>2020</v>
       </c>
       <c r="B7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C7">
         <v>4</v>
       </c>
       <c r="D7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E7">
         <v>159128</v>
       </c>
       <c r="F7">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="G7">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="H7">
         <v>2.5</v>
@@ -583,22 +583,22 @@
         <v>2022</v>
       </c>
       <c r="B9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C9">
         <v>13</v>
       </c>
       <c r="D9">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E9">
         <v>190641</v>
       </c>
       <c r="F9">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="G9">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="H9">
         <v>6.8</v>
@@ -661,25 +661,25 @@
         <v>2025</v>
       </c>
       <c r="B12">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C12">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D12">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E12">
         <v>201500</v>
       </c>
       <c r="F12">
-        <v>6.5</v>
+        <v>7.9</v>
       </c>
       <c r="G12">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="H12">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
     </row>
   </sheetData>

--- a/Salidas/tabla_resumen.xlsx
+++ b/Salidas/tabla_resumen.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -398,287 +398,209 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>2006</v>
+        <v>2018</v>
       </c>
       <c r="B2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C2">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="E2">
-        <v>115400</v>
+        <v>152582</v>
       </c>
       <c r="F2">
-        <v>0.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="G2">
-        <v>0.9</v>
+        <v>2.6</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="3">
       <c r="A3">
-        <v>2014</v>
+        <v>2019</v>
       </c>
       <c r="B3">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="E3">
-        <v>139734</v>
+        <v>155845</v>
       </c>
       <c r="F3">
-        <v>0.7</v>
+        <v>11.5</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="H3">
-        <v>0.7</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4">
-        <v>2017</v>
+        <v>2020</v>
       </c>
       <c r="B4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D4">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E4">
-        <v>149340</v>
+        <v>159128</v>
       </c>
       <c r="F4">
-        <v>2.7</v>
+        <v>5</v>
       </c>
       <c r="G4">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="H4">
-        <v>0.7</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5">
-        <v>2018</v>
+        <v>2021</v>
       </c>
       <c r="B5">
         <v>4</v>
       </c>
       <c r="C5">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D5">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E5">
-        <v>152582</v>
+        <v>162431</v>
       </c>
       <c r="F5">
-        <v>9.199999999999999</v>
+        <v>3.1</v>
       </c>
       <c r="G5">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="H5">
-        <v>6.6</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="6">
       <c r="A6">
-        <v>2019</v>
+        <v>2022</v>
       </c>
       <c r="B6">
+        <v>6</v>
+      </c>
+      <c r="C6">
+        <v>13</v>
+      </c>
+      <c r="D6">
+        <v>19</v>
+      </c>
+      <c r="E6">
+        <v>190641</v>
+      </c>
+      <c r="F6">
         <v>10</v>
       </c>
-      <c r="C6">
-        <v>8</v>
-      </c>
-      <c r="D6">
-        <v>18</v>
-      </c>
-      <c r="E6">
-        <v>155845</v>
-      </c>
-      <c r="F6">
-        <v>11.5</v>
-      </c>
       <c r="G6">
-        <v>6.4</v>
+        <v>3.1</v>
       </c>
       <c r="H6">
-        <v>5.1</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="7">
       <c r="A7">
-        <v>2020</v>
+        <v>2023</v>
       </c>
       <c r="B7">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C7">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="D7">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="E7">
-        <v>159128</v>
+        <v>194200</v>
       </c>
       <c r="F7">
-        <v>5</v>
+        <v>11.3</v>
       </c>
       <c r="G7">
-        <v>2.5</v>
+        <v>3.6</v>
       </c>
       <c r="H7">
-        <v>2.5</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="8">
       <c r="A8">
-        <v>2021</v>
+        <v>2024</v>
       </c>
       <c r="B8">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C8">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D8">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="E8">
-        <v>162431</v>
+        <v>197820</v>
       </c>
       <c r="F8">
-        <v>3.1</v>
+        <v>8.6</v>
       </c>
       <c r="G8">
         <v>2.5</v>
       </c>
       <c r="H8">
-        <v>0.6</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9">
-        <v>2022</v>
+        <v>2025</v>
       </c>
       <c r="B9">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C9">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D9">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E9">
-        <v>190641</v>
+        <v>201500</v>
       </c>
       <c r="F9">
-        <v>10</v>
+        <v>7.9</v>
       </c>
       <c r="G9">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="H9">
-        <v>6.8</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10">
-        <v>2023</v>
-      </c>
-      <c r="B10">
-        <v>7</v>
-      </c>
-      <c r="C10">
-        <v>15</v>
-      </c>
-      <c r="D10">
-        <v>22</v>
-      </c>
-      <c r="E10">
-        <v>194200</v>
-      </c>
-      <c r="F10">
-        <v>11.3</v>
-      </c>
-      <c r="G10">
-        <v>3.6</v>
-      </c>
-      <c r="H10">
-        <v>7.7</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11">
-        <v>2024</v>
-      </c>
-      <c r="B11">
-        <v>5</v>
-      </c>
-      <c r="C11">
-        <v>12</v>
-      </c>
-      <c r="D11">
-        <v>17</v>
-      </c>
-      <c r="E11">
-        <v>197820</v>
-      </c>
-      <c r="F11">
-        <v>8.6</v>
-      </c>
-      <c r="G11">
-        <v>2.5</v>
-      </c>
-      <c r="H11">
-        <v>6.1</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12">
-        <v>2025</v>
-      </c>
-      <c r="B12">
-        <v>7</v>
-      </c>
-      <c r="C12">
-        <v>9</v>
-      </c>
-      <c r="D12">
-        <v>16</v>
-      </c>
-      <c r="E12">
-        <v>201500</v>
-      </c>
-      <c r="F12">
-        <v>7.9</v>
-      </c>
-      <c r="G12">
-        <v>3.5</v>
-      </c>
-      <c r="H12">
         <v>4.5</v>
       </c>
     </row>
